--- a/artfynd/A 15051-2024 artfynd.xlsx
+++ b/artfynd/A 15051-2024 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>207962</v>
+        <v>116705064</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Rödingsjön, Ås lm</t>
+          <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536146.5047844289</v>
+        <v>536213</v>
       </c>
       <c r="R2" t="n">
-        <v>7193863.729314937</v>
+        <v>7193875</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>372675</v>
+        <v>207962</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536146.5047844289</v>
+        <v>536147</v>
       </c>
       <c r="R3" t="n">
-        <v>7193863.729314937</v>
+        <v>7193864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +850,9 @@
           <t>2012-08-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-08-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,53 +884,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>395404</v>
+        <v>116705116</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Rödingsjön, Ås lm</t>
+          <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536151.2694279477</v>
+        <v>536108</v>
       </c>
       <c r="R4" t="n">
-        <v>7193856.982908274</v>
+        <v>7193860</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,21 +975,16 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1029,12 +994,7 @@
         <v>415599</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536151.2694279477</v>
+        <v>536151</v>
       </c>
       <c r="R5" t="n">
-        <v>7193856.982908274</v>
+        <v>7193857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1059,9 @@
           <t>2012-08-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-08-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116705154</v>
+        <v>116705069</v>
       </c>
       <c r="B6" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536113</v>
+        <v>536079</v>
       </c>
       <c r="R6" t="n">
-        <v>7193852</v>
+        <v>7193823</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,58 +1200,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116705081</v>
+        <v>372675</v>
       </c>
       <c r="B7" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rödingsjön, Fjällboberg, Ås lm</t>
+          <t>V Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536322</v>
+        <v>536147</v>
       </c>
       <c r="R7" t="n">
-        <v>7193770</v>
+        <v>7193864</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,22 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2012-08-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2012-08-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,31 +1281,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116705159</v>
+        <v>395404</v>
       </c>
       <c r="B8" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,37 +1313,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödingsjön, Fjällboberg, Ås lm</t>
+          <t>V Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536326</v>
+        <v>536151</v>
       </c>
       <c r="R8" t="n">
-        <v>7193710</v>
+        <v>7193857</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,22 +1367,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2012-08-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2012-08-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,31 +1383,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116705116</v>
+        <v>116705167</v>
       </c>
       <c r="B9" t="n">
-        <v>90444</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536108</v>
+        <v>536324</v>
       </c>
       <c r="R9" t="n">
-        <v>7193860</v>
+        <v>7193714</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1474,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1484,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,37 +1511,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116705156</v>
+        <v>116705075</v>
       </c>
       <c r="B10" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536204</v>
+        <v>536131</v>
       </c>
       <c r="R10" t="n">
-        <v>7193874</v>
+        <v>7193882</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,7 +1581,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1591,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,19 +1618,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116705160</v>
+        <v>116705154</v>
       </c>
       <c r="B11" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1748,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536313</v>
+        <v>536113</v>
       </c>
       <c r="R11" t="n">
-        <v>7193707</v>
+        <v>7193852</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1783,7 +1688,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1698,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,19 +1725,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116705162</v>
+        <v>116705155</v>
       </c>
       <c r="B12" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1860,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536325</v>
+        <v>536174</v>
       </c>
       <c r="R12" t="n">
-        <v>7193693</v>
+        <v>7193876</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,7 +1795,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1805,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,37 +1832,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116705167</v>
+        <v>116705156</v>
       </c>
       <c r="B13" t="n">
-        <v>82217</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536324</v>
+        <v>536204</v>
       </c>
       <c r="R13" t="n">
-        <v>7193714</v>
+        <v>7193874</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +1902,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +1912,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,37 +1939,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116705108</v>
+        <v>116705157</v>
       </c>
       <c r="B14" t="n">
-        <v>77377</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536213</v>
+        <v>536221</v>
       </c>
       <c r="R14" t="n">
-        <v>7193875</v>
+        <v>7193886</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2009,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2019,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,37 +2046,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116705119</v>
+        <v>116705158</v>
       </c>
       <c r="B15" t="n">
-        <v>90466</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536315</v>
+        <v>536299</v>
       </c>
       <c r="R15" t="n">
-        <v>7193705</v>
+        <v>7193781</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2116,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2126,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,37 +2153,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116705064</v>
+        <v>116705159</v>
       </c>
       <c r="B16" t="n">
-        <v>77387</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536213</v>
+        <v>536326</v>
       </c>
       <c r="R16" t="n">
-        <v>7193875</v>
+        <v>7193710</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2223,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2233,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,19 +2260,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116705155</v>
+        <v>116705160</v>
       </c>
       <c r="B17" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2420,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536174</v>
+        <v>536313</v>
       </c>
       <c r="R17" t="n">
-        <v>7193876</v>
+        <v>7193707</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,37 +2367,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116705075</v>
+        <v>116705162</v>
       </c>
       <c r="B18" t="n">
-        <v>91139</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536131</v>
+        <v>536325</v>
       </c>
       <c r="R18" t="n">
-        <v>7193882</v>
+        <v>7193693</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2437,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2447,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,15 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116705158</v>
+        <v>116705067</v>
       </c>
       <c r="B19" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536299</v>
+        <v>536214</v>
       </c>
       <c r="R19" t="n">
-        <v>7193781</v>
+        <v>7193872</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,12 +2584,7 @@
         <v>116705068</v>
       </c>
       <c r="B20" t="n">
-        <v>74553</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,15 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116705157</v>
+        <v>116705081</v>
       </c>
       <c r="B21" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,34 +2699,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536221</v>
+        <v>536322</v>
       </c>
       <c r="R21" t="n">
-        <v>7193886</v>
+        <v>7193770</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2903,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,15 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116705067</v>
+        <v>116705082</v>
       </c>
       <c r="B22" t="n">
-        <v>74553</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2956,34 +2811,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536214</v>
+        <v>536354</v>
       </c>
       <c r="R22" t="n">
-        <v>7193872</v>
+        <v>7193697</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3015,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,15 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>116705082</v>
+        <v>116705108</v>
       </c>
       <c r="B23" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,39 +2923,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536354</v>
+        <v>536213</v>
       </c>
       <c r="R23" t="n">
-        <v>7193697</v>
+        <v>7193875</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3132,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3142,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
